--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314804</v>
       </c>
       <c r="B2" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>131314807</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314793</v>
+        <v>131314701</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497983</v>
+        <v>498259</v>
       </c>
       <c r="R5" t="n">
-        <v>6980361</v>
+        <v>6980592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
         <v>131314707</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314701</v>
+        <v>131314793</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498259</v>
+        <v>497983</v>
       </c>
       <c r="R7" t="n">
-        <v>6980592</v>
+        <v>6980361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1694,7 +1694,7 @@
         <v>131314704</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131314769</v>
       </c>
       <c r="B11" t="n">
-        <v>83225</v>
+        <v>83226</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>131314703</v>
       </c>
       <c r="B13" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>131314706</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>131314705</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131314806</v>
       </c>
       <c r="B34" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314701</v>
+        <v>131314707</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,31 +1046,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498259</v>
+        <v>498243</v>
       </c>
       <c r="R5" t="n">
-        <v>6980592</v>
+        <v>6980541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1122,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1145,14 +1141,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>57881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,26 +1172,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1208,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R6" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,7 +1253,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1276,9 +1271,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,29 +1944,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R12" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2016,7 +2011,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,6 +2020,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2033,6 +2029,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2045,12 +2046,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2068,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,24 +2080,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2106,10 +2112,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R13" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,7 +2152,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,7 +2161,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2164,11 +2169,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314804</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131314803</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>131314807</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,26 +1046,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R5" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1127,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,9 +1145,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1161,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314701</v>
+        <v>131314793</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,16 +1181,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1204,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498259</v>
+        <v>497983</v>
       </c>
       <c r="R6" t="n">
-        <v>6980592</v>
+        <v>6980361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1253,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,12 +1282,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314793</v>
+        <v>131314707</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,31 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497983</v>
+        <v>498243</v>
       </c>
       <c r="R7" t="n">
-        <v>6980361</v>
+        <v>6980541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,6 +1392,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1406,14 +1411,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
         <v>131314791</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>131314792</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>131314704</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131314769</v>
       </c>
       <c r="B11" t="n">
-        <v>83226</v>
+        <v>83228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>131314706</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>131314705</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>131314781</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>131314787</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>131314777</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>131314782</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>131314785</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>131314780</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>131314839</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>131314786</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>131314778</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>131314789</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131314773</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>131314788</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>131314790</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314779</v>
+        <v>131314783</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498295</v>
+        <v>498390</v>
       </c>
       <c r="R29" t="n">
-        <v>6980533</v>
+        <v>6980556</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131314783</v>
+        <v>131314779</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498390</v>
+        <v>498295</v>
       </c>
       <c r="R30" t="n">
-        <v>6980556</v>
+        <v>6980533</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
         <v>131314775</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131314784</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131314774</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131314806</v>
       </c>
       <c r="B34" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>131314776</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314804</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131314803</v>
       </c>
       <c r="B3" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>131314807</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314701</v>
+        <v>131314707</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,31 +1046,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498259</v>
+        <v>498243</v>
       </c>
       <c r="R5" t="n">
-        <v>6980592</v>
+        <v>6980541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1122,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1145,14 +1141,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,7 +1164,7 @@
         <v>131314793</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1307,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R7" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1388,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1411,9 +1406,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
         <v>131314791</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>131314792</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>131314704</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131314769</v>
       </c>
       <c r="B11" t="n">
-        <v>83228</v>
+        <v>83229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B12" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,24 +1944,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1971,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R12" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2011,7 +2016,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,7 +2025,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2029,11 +2033,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2046,12 +2045,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2069,10 +2068,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,29 +2079,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2112,10 +2106,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R13" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2152,7 +2146,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2161,6 +2155,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2169,6 +2164,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
         <v>131314706</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>131314705</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>131314781</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>131314787</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>131314777</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>131314782</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>131314785</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>131314780</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>131314839</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>131314786</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>131314778</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>131314789</v>
       </c>
       <c r="B25" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131314773</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>131314788</v>
       </c>
       <c r="B27" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>131314790</v>
       </c>
       <c r="B28" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314783</v>
+        <v>131314779</v>
       </c>
       <c r="B29" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498390</v>
+        <v>498295</v>
       </c>
       <c r="R29" t="n">
-        <v>6980556</v>
+        <v>6980533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131314779</v>
+        <v>131314783</v>
       </c>
       <c r="B30" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498295</v>
+        <v>498390</v>
       </c>
       <c r="R30" t="n">
-        <v>6980533</v>
+        <v>6980556</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
         <v>131314775</v>
       </c>
       <c r="B31" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131314784</v>
       </c>
       <c r="B32" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131314774</v>
       </c>
       <c r="B33" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131314806</v>
       </c>
       <c r="B34" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>131314776</v>
       </c>
       <c r="B35" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,26 +1046,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R5" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1127,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,9 +1145,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1296,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314701</v>
+        <v>131314707</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,31 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498259</v>
+        <v>498243</v>
       </c>
       <c r="R7" t="n">
-        <v>6980592</v>
+        <v>6980541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,6 +1392,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1406,14 +1411,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,29 +1944,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R12" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2016,7 +2011,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,6 +2020,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2033,6 +2029,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2045,12 +2046,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2068,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,24 +2080,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2106,10 +2112,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R13" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,7 +2152,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,7 +2161,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2164,11 +2169,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314778</v>
+        <v>131314789</v>
       </c>
       <c r="B24" t="n">
         <v>57887</v>
@@ -3529,7 +3529,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498277</v>
+        <v>498066</v>
       </c>
       <c r="R24" t="n">
-        <v>6980549</v>
+        <v>6980381</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3606,9 +3606,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3626,7 +3631,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314789</v>
+        <v>131314778</v>
       </c>
       <c r="B25" t="n">
         <v>57887</v>
@@ -3659,7 +3664,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3669,10 +3674,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498066</v>
+        <v>498277</v>
       </c>
       <c r="R25" t="n">
-        <v>6980381</v>
+        <v>6980549</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,7 +3714,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3736,14 +3741,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314701</v>
+        <v>131314707</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,31 +1046,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498259</v>
+        <v>498243</v>
       </c>
       <c r="R5" t="n">
-        <v>6980592</v>
+        <v>6980541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1122,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1145,14 +1141,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1307,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R7" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1388,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1411,9 +1406,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B12" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,24 +1944,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1971,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R12" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2011,7 +2016,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,7 +2025,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2029,11 +2033,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2046,12 +2045,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2069,10 +2068,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,29 +2079,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2112,10 +2106,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R13" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2152,7 +2146,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2161,6 +2155,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2169,6 +2164,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314789</v>
+        <v>131314778</v>
       </c>
       <c r="B24" t="n">
         <v>57887</v>
@@ -3529,7 +3529,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498066</v>
+        <v>498277</v>
       </c>
       <c r="R24" t="n">
-        <v>6980381</v>
+        <v>6980549</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3606,14 +3606,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3631,7 +3626,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314778</v>
+        <v>131314789</v>
       </c>
       <c r="B25" t="n">
         <v>57887</v>
@@ -3664,7 +3659,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3674,10 +3669,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498277</v>
+        <v>498066</v>
       </c>
       <c r="R25" t="n">
-        <v>6980549</v>
+        <v>6980381</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3714,7 +3709,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3741,9 +3736,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314804</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>131314807</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131314707</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314793</v>
+        <v>131314701</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497983</v>
+        <v>498259</v>
       </c>
       <c r="R6" t="n">
-        <v>6980361</v>
+        <v>6980592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314701</v>
+        <v>131314793</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498259</v>
+        <v>497983</v>
       </c>
       <c r="R7" t="n">
-        <v>6980592</v>
+        <v>6980361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
         <v>131314791</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>131314792</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>131314704</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131314769</v>
       </c>
       <c r="B11" t="n">
-        <v>83229</v>
+        <v>83230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,29 +1944,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R12" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2016,7 +2011,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,6 +2020,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2033,6 +2029,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2045,12 +2046,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2068,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,24 +2080,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2106,10 +2112,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R13" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,7 +2152,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,7 +2161,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2164,11 +2169,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
         <v>131314706</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>131314705</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>131314781</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>131314787</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>131314777</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>131314782</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>131314785</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>131314780</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>131314839</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>131314786</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>131314778</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>131314789</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131314773</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>131314788</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>131314790</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>131314779</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>131314783</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>131314775</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131314784</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131314774</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131314806</v>
       </c>
       <c r="B34" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>131314776</v>
       </c>
       <c r="B35" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,26 +1046,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R5" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1127,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,9 +1145,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1161,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314701</v>
+        <v>131314793</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,16 +1181,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1204,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498259</v>
+        <v>497983</v>
       </c>
       <c r="R6" t="n">
-        <v>6980592</v>
+        <v>6980361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1253,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,12 +1282,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314793</v>
+        <v>131314707</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,31 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497983</v>
+        <v>498243</v>
       </c>
       <c r="R7" t="n">
-        <v>6980361</v>
+        <v>6980541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,6 +1392,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1406,14 +1411,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,24 +1944,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1971,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R12" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2011,7 +2016,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,7 +2025,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2029,11 +2033,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2046,12 +2045,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2069,10 +2068,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,29 +2079,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2112,10 +2106,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R13" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2152,7 +2146,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2161,6 +2155,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2169,6 +2164,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314701</v>
+        <v>131314793</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498259</v>
+        <v>497983</v>
       </c>
       <c r="R5" t="n">
-        <v>6980592</v>
+        <v>6980361</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314793</v>
+        <v>131314707</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,31 +1181,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1213,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497983</v>
+        <v>498243</v>
       </c>
       <c r="R6" t="n">
-        <v>6980361</v>
+        <v>6980541</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,7 +1248,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,6 +1257,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1280,14 +1276,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1307,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R7" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1388,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1411,9 +1406,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314804</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131314803</v>
       </c>
       <c r="B3" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>131314807</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314793</v>
+        <v>131314701</v>
       </c>
       <c r="B5" t="n">
         <v>57888</v>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497983</v>
+        <v>498259</v>
       </c>
       <c r="R5" t="n">
-        <v>6980361</v>
+        <v>6980592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314707</v>
+        <v>131314793</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,26 +1181,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1208,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498243</v>
+        <v>497983</v>
       </c>
       <c r="R6" t="n">
-        <v>6980541</v>
+        <v>6980361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1253,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,7 +1262,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1276,9 +1280,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314701</v>
+        <v>131314707</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,31 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498259</v>
+        <v>498243</v>
       </c>
       <c r="R7" t="n">
-        <v>6980592</v>
+        <v>6980541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,6 +1392,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1406,14 +1411,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314791</v>
+        <v>131314792</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498065</v>
+        <v>497998</v>
       </c>
       <c r="R8" t="n">
-        <v>6980378</v>
+        <v>6980370</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314792</v>
+        <v>131314791</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497998</v>
+        <v>498065</v>
       </c>
       <c r="R9" t="n">
-        <v>6980370</v>
+        <v>6980378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,7 +1694,7 @@
         <v>131314704</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131314769</v>
       </c>
       <c r="B11" t="n">
-        <v>83230</v>
+        <v>83233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>91841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,29 +1944,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R12" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2016,7 +2011,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,6 +2020,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2033,6 +2029,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2045,12 +2046,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2068,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>91838</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,24 +2080,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2106,10 +2112,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R13" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,7 +2152,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,7 +2161,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2164,11 +2169,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
         <v>131314706</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>131314705</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>131314781</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>131314787</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>131314777</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>131314782</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>131314785</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>131314780</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>131314839</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3366,10 +3366,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314786</v>
+        <v>131314778</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498353</v>
+        <v>498277</v>
       </c>
       <c r="R23" t="n">
-        <v>6980511</v>
+        <v>6980549</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3496,10 +3496,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314778</v>
+        <v>131314789</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498277</v>
+        <v>498066</v>
       </c>
       <c r="R24" t="n">
-        <v>6980549</v>
+        <v>6980381</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3606,9 +3606,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3626,10 +3631,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314789</v>
+        <v>131314786</v>
       </c>
       <c r="B25" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3659,7 +3664,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3669,10 +3674,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498066</v>
+        <v>498353</v>
       </c>
       <c r="R25" t="n">
-        <v>6980381</v>
+        <v>6980511</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,7 +3714,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3736,14 +3741,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3764,7 +3764,7 @@
         <v>131314773</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>131314788</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>131314790</v>
       </c>
       <c r="B28" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314779</v>
+        <v>131314775</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498295</v>
+        <v>498126</v>
       </c>
       <c r="R29" t="n">
-        <v>6980533</v>
+        <v>6980530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4289,7 +4289,7 @@
         <v>131314783</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4416,10 +4416,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131314775</v>
+        <v>131314779</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>498126</v>
+        <v>498295</v>
       </c>
       <c r="R31" t="n">
-        <v>6980530</v>
+        <v>6980533</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4549,7 +4549,7 @@
         <v>131314784</v>
       </c>
       <c r="B32" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131314774</v>
       </c>
       <c r="B33" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131314806</v>
       </c>
       <c r="B34" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>131314776</v>
       </c>
       <c r="B35" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314804</v>
+        <v>131314803</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>57071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498371</v>
+        <v>498066</v>
       </c>
       <c r="R2" t="n">
-        <v>6980561</v>
+        <v>6980662</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,28 +770,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314803</v>
+        <v>131314804</v>
       </c>
       <c r="B3" t="n">
-        <v>57070</v>
+        <v>91842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,50 +804,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498066</v>
+        <v>498371</v>
       </c>
       <c r="R3" t="n">
-        <v>6980662</v>
+        <v>6980561</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,12 +875,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,7 +917,7 @@
         <v>131314807</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131314701</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314793</v>
+        <v>131314707</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,31 +1181,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1213,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497983</v>
+        <v>498243</v>
       </c>
       <c r="R6" t="n">
-        <v>6980361</v>
+        <v>6980541</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,7 +1248,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,6 +1257,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1280,14 +1276,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314707</v>
+        <v>131314793</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1307,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498243</v>
+        <v>497983</v>
       </c>
       <c r="R7" t="n">
-        <v>6980541</v>
+        <v>6980361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1388,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1411,9 +1406,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314792</v>
+        <v>131314791</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497998</v>
+        <v>498065</v>
       </c>
       <c r="R8" t="n">
-        <v>6980370</v>
+        <v>6980378</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314791</v>
+        <v>131314792</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498065</v>
+        <v>497998</v>
       </c>
       <c r="R9" t="n">
-        <v>6980378</v>
+        <v>6980370</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,7 +1694,7 @@
         <v>131314704</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131314769</v>
       </c>
       <c r="B11" t="n">
-        <v>83233</v>
+        <v>83234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>131314706</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>131314705</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>131314781</v>
       </c>
       <c r="B16" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>131314787</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>131314777</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>131314782</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>131314785</v>
       </c>
       <c r="B20" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>131314780</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>131314839</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>131314778</v>
       </c>
       <c r="B23" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>131314789</v>
       </c>
       <c r="B24" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>131314786</v>
       </c>
       <c r="B25" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131314773</v>
       </c>
       <c r="B26" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>131314788</v>
       </c>
       <c r="B27" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>131314790</v>
       </c>
       <c r="B28" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314775</v>
+        <v>131314779</v>
       </c>
       <c r="B29" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498126</v>
+        <v>498295</v>
       </c>
       <c r="R29" t="n">
-        <v>6980530</v>
+        <v>6980533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4289,7 +4289,7 @@
         <v>131314783</v>
       </c>
       <c r="B30" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4416,10 +4416,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131314779</v>
+        <v>131314775</v>
       </c>
       <c r="B31" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>498295</v>
+        <v>498126</v>
       </c>
       <c r="R31" t="n">
-        <v>6980533</v>
+        <v>6980530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4549,7 +4549,7 @@
         <v>131314784</v>
       </c>
       <c r="B32" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131314774</v>
       </c>
       <c r="B33" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131314806</v>
       </c>
       <c r="B34" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>131314776</v>
       </c>
       <c r="B35" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -3366,7 +3366,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314778</v>
+        <v>131314786</v>
       </c>
       <c r="B23" t="n">
         <v>57892</v>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498277</v>
+        <v>498353</v>
       </c>
       <c r="R23" t="n">
-        <v>6980549</v>
+        <v>6980511</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314789</v>
+        <v>131314778</v>
       </c>
       <c r="B24" t="n">
         <v>57892</v>
@@ -3529,7 +3529,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498066</v>
+        <v>498277</v>
       </c>
       <c r="R24" t="n">
-        <v>6980381</v>
+        <v>6980549</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3606,14 +3606,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3631,7 +3626,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314786</v>
+        <v>131314789</v>
       </c>
       <c r="B25" t="n">
         <v>57892</v>
@@ -3664,7 +3659,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3674,10 +3669,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498353</v>
+        <v>498066</v>
       </c>
       <c r="R25" t="n">
-        <v>6980511</v>
+        <v>6980381</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3714,7 +3709,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3741,9 +3736,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314803</v>
+        <v>131314804</v>
       </c>
       <c r="B2" t="n">
-        <v>57071</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498066</v>
+        <v>498371</v>
       </c>
       <c r="R2" t="n">
-        <v>6980662</v>
+        <v>6980561</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,12 +757,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -793,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314804</v>
+        <v>131314803</v>
       </c>
       <c r="B3" t="n">
-        <v>91842</v>
+        <v>57077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,37 +807,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498371</v>
+        <v>498066</v>
       </c>
       <c r="R3" t="n">
-        <v>6980561</v>
+        <v>6980662</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,28 +891,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,7 +917,7 @@
         <v>131314807</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314701</v>
+        <v>131314707</v>
       </c>
       <c r="B5" t="n">
-        <v>57889</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,31 +1046,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498259</v>
+        <v>498243</v>
       </c>
       <c r="R5" t="n">
-        <v>6980592</v>
+        <v>6980541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1122,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1145,14 +1141,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,26 +1172,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1208,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R6" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,7 +1253,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1276,9 +1271,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
         <v>131314793</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>131314791</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>131314792</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>131314704</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131314769</v>
       </c>
       <c r="B11" t="n">
-        <v>83234</v>
+        <v>83240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2204,10 +2204,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314706</v>
+        <v>131314705</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498236</v>
+        <v>498287</v>
       </c>
       <c r="R14" t="n">
-        <v>6980588</v>
+        <v>6980614</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Intill andra hänglavar på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2330,10 +2330,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314705</v>
+        <v>131314706</v>
       </c>
       <c r="B15" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498287</v>
+        <v>498236</v>
       </c>
       <c r="R15" t="n">
-        <v>6980614</v>
+        <v>6980588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Intill andra hänglavar på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2459,7 +2459,7 @@
         <v>131314781</v>
       </c>
       <c r="B16" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>131314787</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>131314777</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>131314782</v>
       </c>
       <c r="B19" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>131314785</v>
       </c>
       <c r="B20" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>131314780</v>
       </c>
       <c r="B21" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>131314839</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>131314786</v>
       </c>
       <c r="B23" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>131314778</v>
       </c>
       <c r="B24" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>131314789</v>
       </c>
       <c r="B25" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131314773</v>
       </c>
       <c r="B26" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>131314788</v>
       </c>
       <c r="B27" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>131314790</v>
       </c>
       <c r="B28" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>131314779</v>
       </c>
       <c r="B29" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>131314783</v>
       </c>
       <c r="B30" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>131314775</v>
       </c>
       <c r="B31" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131314784</v>
       </c>
       <c r="B32" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131314774</v>
       </c>
       <c r="B33" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131314806</v>
       </c>
       <c r="B34" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>131314776</v>
       </c>
       <c r="B35" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B12" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,24 +1944,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1971,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R12" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2011,7 +2016,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,7 +2025,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2029,11 +2033,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2046,12 +2045,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2069,10 +2068,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,29 +2079,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2112,10 +2106,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R13" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2152,7 +2146,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2161,6 +2155,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2169,6 +2164,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314779</v>
+        <v>131314783</v>
       </c>
       <c r="B29" t="n">
         <v>57898</v>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498295</v>
+        <v>498390</v>
       </c>
       <c r="R29" t="n">
-        <v>6980533</v>
+        <v>6980556</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131314783</v>
+        <v>131314779</v>
       </c>
       <c r="B30" t="n">
         <v>57898</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498390</v>
+        <v>498295</v>
       </c>
       <c r="R30" t="n">
-        <v>6980556</v>
+        <v>6980533</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -2716,7 +2716,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314777</v>
+        <v>131314782</v>
       </c>
       <c r="B18" t="n">
         <v>57898</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498308</v>
+        <v>498337</v>
       </c>
       <c r="R18" t="n">
-        <v>6980576</v>
+        <v>6980543</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314782</v>
+        <v>131314777</v>
       </c>
       <c r="B19" t="n">
         <v>57898</v>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498337</v>
+        <v>498308</v>
       </c>
       <c r="R19" t="n">
-        <v>6980543</v>
+        <v>6980576</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,26 +1046,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R5" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1127,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,9 +1145,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1161,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314701</v>
+        <v>131314793</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,16 +1181,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1204,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498259</v>
+        <v>497983</v>
       </c>
       <c r="R6" t="n">
-        <v>6980592</v>
+        <v>6980361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1253,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,12 +1282,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314793</v>
+        <v>131314707</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,31 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497983</v>
+        <v>498243</v>
       </c>
       <c r="R7" t="n">
-        <v>6980361</v>
+        <v>6980541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,6 +1392,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1406,14 +1411,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,29 +1944,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R12" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2016,7 +2011,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,6 +2020,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2033,6 +2029,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2045,12 +2046,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2068,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,24 +2080,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2106,10 +2112,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R13" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,7 +2152,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,7 +2161,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2164,11 +2169,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2204,7 +2204,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314705</v>
+        <v>131314706</v>
       </c>
       <c r="B14" t="n">
         <v>79260</v>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498287</v>
+        <v>498236</v>
       </c>
       <c r="R14" t="n">
-        <v>6980614</v>
+        <v>6980588</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Intill andra hänglavar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2330,7 +2330,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314706</v>
+        <v>131314705</v>
       </c>
       <c r="B15" t="n">
         <v>79260</v>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498236</v>
+        <v>498287</v>
       </c>
       <c r="R15" t="n">
-        <v>6980588</v>
+        <v>6980614</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Intill andra hänglavar på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2716,7 +2716,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314782</v>
+        <v>131314777</v>
       </c>
       <c r="B18" t="n">
         <v>57898</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498337</v>
+        <v>498308</v>
       </c>
       <c r="R18" t="n">
-        <v>6980543</v>
+        <v>6980576</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314777</v>
+        <v>131314782</v>
       </c>
       <c r="B19" t="n">
         <v>57898</v>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498308</v>
+        <v>498337</v>
       </c>
       <c r="R19" t="n">
-        <v>6980576</v>
+        <v>6980543</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314783</v>
+        <v>131314779</v>
       </c>
       <c r="B29" t="n">
         <v>57898</v>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498390</v>
+        <v>498295</v>
       </c>
       <c r="R29" t="n">
-        <v>6980556</v>
+        <v>6980533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131314779</v>
+        <v>131314783</v>
       </c>
       <c r="B30" t="n">
         <v>57898</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498295</v>
+        <v>498390</v>
       </c>
       <c r="R30" t="n">
-        <v>6980533</v>
+        <v>6980556</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314804</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131314803</v>
       </c>
       <c r="B3" t="n">
-        <v>57077</v>
+        <v>57078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>131314807</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314701</v>
+        <v>131314707</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,31 +1046,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498259</v>
+        <v>498243</v>
       </c>
       <c r="R5" t="n">
-        <v>6980592</v>
+        <v>6980541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1122,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1145,14 +1141,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,7 +1164,7 @@
         <v>131314793</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1307,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R7" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1388,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1411,9 +1406,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
         <v>131314791</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>131314792</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>131314704</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131314769</v>
       </c>
       <c r="B11" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>131314706</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>131314705</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>131314781</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>131314787</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>131314777</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>131314782</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>131314785</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>131314780</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>131314839</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>131314786</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>131314778</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>131314789</v>
       </c>
       <c r="B25" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131314773</v>
       </c>
       <c r="B26" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>131314788</v>
       </c>
       <c r="B27" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>131314790</v>
       </c>
       <c r="B28" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>131314779</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>131314783</v>
       </c>
       <c r="B30" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>131314775</v>
       </c>
       <c r="B31" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131314784</v>
       </c>
       <c r="B32" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131314774</v>
       </c>
       <c r="B33" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131314806</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>131314776</v>
       </c>
       <c r="B35" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314804</v>
       </c>
       <c r="B2" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131314803</v>
       </c>
       <c r="B3" t="n">
-        <v>57078</v>
+        <v>57081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>131314807</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131314707</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314793</v>
+        <v>131314701</v>
       </c>
       <c r="B6" t="n">
         <v>57899</v>
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497983</v>
+        <v>498259</v>
       </c>
       <c r="R6" t="n">
-        <v>6980361</v>
+        <v>6980592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314701</v>
+        <v>131314793</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498259</v>
+        <v>497983</v>
       </c>
       <c r="R7" t="n">
-        <v>6980592</v>
+        <v>6980361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
         <v>131314791</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>131314792</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>131314704</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131314769</v>
       </c>
       <c r="B11" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>131314706</v>
       </c>
       <c r="B14" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>131314705</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>131314781</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>131314787</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>131314777</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>131314782</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>131314785</v>
       </c>
       <c r="B20" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>131314780</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>131314839</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>131314786</v>
       </c>
       <c r="B23" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>131314778</v>
       </c>
       <c r="B24" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>131314789</v>
       </c>
       <c r="B25" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131314773</v>
       </c>
       <c r="B26" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>131314788</v>
       </c>
       <c r="B27" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>131314790</v>
       </c>
       <c r="B28" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>131314779</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>131314783</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>131314775</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131314784</v>
       </c>
       <c r="B32" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131314774</v>
       </c>
       <c r="B33" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131314806</v>
       </c>
       <c r="B34" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>131314776</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314804</v>
+        <v>131314803</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>57081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498371</v>
+        <v>498066</v>
       </c>
       <c r="R2" t="n">
-        <v>6980561</v>
+        <v>6980662</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,28 +770,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314803</v>
+        <v>131314804</v>
       </c>
       <c r="B3" t="n">
-        <v>57081</v>
+        <v>91852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,50 +804,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498066</v>
+        <v>498371</v>
       </c>
       <c r="R3" t="n">
-        <v>6980662</v>
+        <v>6980561</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,12 +875,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,26 +1046,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R5" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1127,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,9 +1145,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1161,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314701</v>
+        <v>131314793</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,16 +1181,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1204,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498259</v>
+        <v>497983</v>
       </c>
       <c r="R6" t="n">
-        <v>6980592</v>
+        <v>6980361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1253,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,12 +1282,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314793</v>
+        <v>131314707</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,31 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497983</v>
+        <v>498243</v>
       </c>
       <c r="R7" t="n">
-        <v>6980361</v>
+        <v>6980541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,6 +1392,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1406,14 +1411,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,24 +1944,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1971,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R12" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2011,7 +2016,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,7 +2025,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2029,11 +2033,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2046,12 +2045,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2069,10 +2068,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,29 +2079,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2112,10 +2106,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R13" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2152,7 +2146,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2161,6 +2155,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2169,6 +2164,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314779</v>
+        <v>131314783</v>
       </c>
       <c r="B29" t="n">
         <v>57902</v>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498295</v>
+        <v>498390</v>
       </c>
       <c r="R29" t="n">
-        <v>6980533</v>
+        <v>6980556</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131314783</v>
+        <v>131314775</v>
       </c>
       <c r="B30" t="n">
         <v>57902</v>
@@ -4319,7 +4319,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498390</v>
+        <v>498126</v>
       </c>
       <c r="R30" t="n">
-        <v>6980556</v>
+        <v>6980530</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4416,7 +4416,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131314775</v>
+        <v>131314779</v>
       </c>
       <c r="B31" t="n">
         <v>57902</v>
@@ -4449,7 +4449,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>498126</v>
+        <v>498295</v>
       </c>
       <c r="R31" t="n">
-        <v>6980530</v>
+        <v>6980533</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314803</v>
+        <v>131314804</v>
       </c>
       <c r="B2" t="n">
-        <v>57081</v>
+        <v>91852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498066</v>
+        <v>498371</v>
       </c>
       <c r="R2" t="n">
-        <v>6980662</v>
+        <v>6980561</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,12 +757,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -793,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314804</v>
+        <v>131314803</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>57081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,37 +807,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498371</v>
+        <v>498066</v>
       </c>
       <c r="R3" t="n">
-        <v>6980561</v>
+        <v>6980662</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,28 +891,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314793</v>
+        <v>131314707</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,31 +1181,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1213,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497983</v>
+        <v>498243</v>
       </c>
       <c r="R6" t="n">
-        <v>6980361</v>
+        <v>6980541</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,7 +1248,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,6 +1257,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1280,14 +1276,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314707</v>
+        <v>131314793</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1307,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498243</v>
+        <v>497983</v>
       </c>
       <c r="R7" t="n">
-        <v>6980541</v>
+        <v>6980361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1388,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1411,9 +1406,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,29 +1944,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R12" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2016,7 +2011,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,6 +2020,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2033,6 +2029,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2045,12 +2046,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2068,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,24 +2080,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2106,10 +2112,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R13" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,7 +2152,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,7 +2161,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2164,11 +2169,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314783</v>
+        <v>131314779</v>
       </c>
       <c r="B29" t="n">
         <v>57902</v>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498390</v>
+        <v>498295</v>
       </c>
       <c r="R29" t="n">
-        <v>6980556</v>
+        <v>6980533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131314775</v>
+        <v>131314783</v>
       </c>
       <c r="B30" t="n">
         <v>57902</v>
@@ -4319,7 +4319,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498126</v>
+        <v>498390</v>
       </c>
       <c r="R30" t="n">
-        <v>6980530</v>
+        <v>6980556</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4416,7 +4416,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131314779</v>
+        <v>131314775</v>
       </c>
       <c r="B31" t="n">
         <v>57902</v>
@@ -4449,7 +4449,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>498295</v>
+        <v>498126</v>
       </c>
       <c r="R31" t="n">
-        <v>6980533</v>
+        <v>6980530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314701</v>
+        <v>131314707</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,31 +1046,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498259</v>
+        <v>498243</v>
       </c>
       <c r="R5" t="n">
-        <v>6980592</v>
+        <v>6980541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1122,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1145,14 +1141,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,26 +1172,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1208,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R6" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,7 +1253,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1276,9 +1271,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314804</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>131314803</v>
       </c>
       <c r="B3" t="n">
-        <v>57081</v>
+        <v>57083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>131314807</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314707</v>
+        <v>131314701</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,26 +1046,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498243</v>
+        <v>498259</v>
       </c>
       <c r="R5" t="n">
-        <v>6980541</v>
+        <v>6980592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1118,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1127,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,9 +1145,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1161,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314701</v>
+        <v>131314793</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,16 +1181,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1204,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498259</v>
+        <v>497983</v>
       </c>
       <c r="R6" t="n">
-        <v>6980592</v>
+        <v>6980361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1253,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,12 +1282,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314793</v>
+        <v>131314707</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,31 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497983</v>
+        <v>498243</v>
       </c>
       <c r="R7" t="n">
-        <v>6980361</v>
+        <v>6980541</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,6 +1392,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1406,14 +1411,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314791</v>
+        <v>131314792</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498065</v>
+        <v>497998</v>
       </c>
       <c r="R8" t="n">
-        <v>6980378</v>
+        <v>6980370</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314792</v>
+        <v>131314791</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497998</v>
+        <v>498065</v>
       </c>
       <c r="R9" t="n">
-        <v>6980370</v>
+        <v>6980378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1694,7 +1694,7 @@
         <v>131314704</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131314769</v>
       </c>
       <c r="B11" t="n">
-        <v>83244</v>
+        <v>83246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>131314703</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>131314697</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>131314706</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>131314705</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>131314781</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>131314787</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314777</v>
+        <v>131314782</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498308</v>
+        <v>498337</v>
       </c>
       <c r="R18" t="n">
-        <v>6980576</v>
+        <v>6980543</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314782</v>
+        <v>131314777</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498337</v>
+        <v>498308</v>
       </c>
       <c r="R19" t="n">
-        <v>6980543</v>
+        <v>6980576</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2979,7 +2979,7 @@
         <v>131314785</v>
       </c>
       <c r="B20" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>131314780</v>
       </c>
       <c r="B21" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>131314839</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>131314786</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>131314778</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>131314789</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131314773</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>131314788</v>
       </c>
       <c r="B27" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>131314790</v>
       </c>
       <c r="B28" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>131314779</v>
       </c>
       <c r="B29" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>131314783</v>
       </c>
       <c r="B30" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>131314775</v>
       </c>
       <c r="B31" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131314784</v>
       </c>
       <c r="B32" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131314774</v>
       </c>
       <c r="B33" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>131314806</v>
       </c>
       <c r="B34" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>131314776</v>
       </c>
       <c r="B35" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -1933,10 +1933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314703</v>
+        <v>131314697</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,24 +1944,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1971,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498222</v>
+        <v>498259</v>
       </c>
       <c r="R12" t="n">
-        <v>6980602</v>
+        <v>6980588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2011,7 +2016,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,7 +2025,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2029,11 +2033,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2046,12 +2045,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2069,10 +2068,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314697</v>
+        <v>131314703</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,29 +2079,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2112,10 +2106,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498259</v>
+        <v>498222</v>
       </c>
       <c r="R13" t="n">
-        <v>6980588</v>
+        <v>6980602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2152,7 +2146,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Flera fruktkroppar i en klen stående död gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2161,6 +2155,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2169,6 +2164,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314782</v>
+        <v>131314777</v>
       </c>
       <c r="B18" t="n">
         <v>57904</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498337</v>
+        <v>498308</v>
       </c>
       <c r="R18" t="n">
-        <v>6980543</v>
+        <v>6980576</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314777</v>
+        <v>131314782</v>
       </c>
       <c r="B19" t="n">
         <v>57904</v>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498308</v>
+        <v>498337</v>
       </c>
       <c r="R19" t="n">
-        <v>6980576</v>
+        <v>6980543</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314701</v>
+        <v>131314707</v>
       </c>
       <c r="B5" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,31 +1046,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498259</v>
+        <v>498243</v>
       </c>
       <c r="R5" t="n">
-        <v>6980592</v>
+        <v>6980541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1122,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1145,14 +1141,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314793</v>
+        <v>131314701</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>57901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,16 +1172,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1213,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497983</v>
+        <v>498259</v>
       </c>
       <c r="R6" t="n">
-        <v>6980361</v>
+        <v>6980592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,7 +1244,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,12 +1273,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314707</v>
+        <v>131314793</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,26 +1307,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498243</v>
+        <v>497983</v>
       </c>
       <c r="R7" t="n">
-        <v>6980541</v>
+        <v>6980361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1388,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1411,9 +1406,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 60623-2022 artfynd.xlsx
+++ b/artfynd/A 60623-2022 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314804</v>
+        <v>131314704</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498371</v>
+        <v>498074</v>
       </c>
       <c r="R2" t="n">
-        <v>6980561</v>
+        <v>6980666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,61 +796,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314803</v>
+        <v>131314705</v>
       </c>
       <c r="B3" t="n">
-        <v>57083</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498066</v>
+        <v>498287</v>
       </c>
       <c r="R3" t="n">
-        <v>6980662</v>
+        <v>6980614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,18 +872,39 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,14 +922,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131314807</v>
+        <v>131314706</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -952,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498320</v>
+        <v>498236</v>
       </c>
       <c r="R4" t="n">
-        <v>6980482</v>
+        <v>6980588</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,6 +996,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Intill andra hänglavar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,11 +1051,11 @@
         <v>131314707</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1161,42 +1174,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314701</v>
+        <v>131314806</v>
       </c>
       <c r="B6" t="n">
-        <v>57901</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1204,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498259</v>
+        <v>498220</v>
       </c>
       <c r="R6" t="n">
-        <v>6980592</v>
+        <v>6980720</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,17 +1250,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1271,14 +1275,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,42 +1295,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314793</v>
+        <v>131314807</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1339,10 +1333,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497983</v>
+        <v>498320</v>
       </c>
       <c r="R7" t="n">
-        <v>6980361</v>
+        <v>6980482</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,17 +1371,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1406,14 +1396,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1431,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314792</v>
+        <v>131314769</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,31 +1427,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1474,10 +1454,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497998</v>
+        <v>498316</v>
       </c>
       <c r="R8" t="n">
-        <v>6980370</v>
+        <v>6980501</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,17 +1492,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1561,27 +1537,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314791</v>
+        <v>131314701</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1604,10 +1580,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498065</v>
+        <v>498259</v>
       </c>
       <c r="R9" t="n">
-        <v>6980378</v>
+        <v>6980592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1644,7 +1620,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Rejäla hackspår, färska och äldre, i stambasen av en stående död gran med 41 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,9 +1647,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1691,10 +1672,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314704</v>
+        <v>131314697</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,26 +1683,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1729,10 +1715,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498074</v>
+        <v>498259</v>
       </c>
       <c r="R10" t="n">
-        <v>6980666</v>
+        <v>6980588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1767,13 +1753,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1792,9 +1782,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1812,10 +1807,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314769</v>
+        <v>131314698</v>
       </c>
       <c r="B11" t="n">
-        <v>83246</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,26 +1818,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498316</v>
+        <v>497905</v>
       </c>
       <c r="R11" t="n">
-        <v>6980501</v>
+        <v>6980339</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1888,13 +1888,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1913,9 +1917,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1933,10 +1942,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314697</v>
+        <v>131314773</v>
       </c>
       <c r="B12" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1975,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1976,10 +1985,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498259</v>
+        <v>498125</v>
       </c>
       <c r="R12" t="n">
-        <v>6980588</v>
+        <v>6980508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2016,7 +2025,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka några meter upp på en gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2043,14 +2052,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2068,10 +2072,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314703</v>
+        <v>131314774</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,24 +2083,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2106,10 +2115,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498222</v>
+        <v>498124</v>
       </c>
       <c r="R13" t="n">
-        <v>6980602</v>
+        <v>6980534</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,7 +2155,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en klen stående död gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,7 +2164,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2164,11 +2172,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2179,14 +2182,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2204,10 +2202,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314706</v>
+        <v>131314775</v>
       </c>
       <c r="B14" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,26 +2213,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2242,10 +2245,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498236</v>
+        <v>498126</v>
       </c>
       <c r="R14" t="n">
-        <v>6980588</v>
+        <v>6980530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2282,7 +2285,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Intill andra hänglavar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,7 +2294,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2330,10 +2332,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314705</v>
+        <v>131314776</v>
       </c>
       <c r="B15" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,26 +2343,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2368,10 +2375,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498287</v>
+        <v>498176</v>
       </c>
       <c r="R15" t="n">
-        <v>6980614</v>
+        <v>6980749</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2408,7 +2415,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2417,7 +2424,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2456,10 +2462,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314781</v>
+        <v>131314777</v>
       </c>
       <c r="B16" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,10 +2505,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498293</v>
+        <v>498308</v>
       </c>
       <c r="R16" t="n">
-        <v>6980509</v>
+        <v>6980576</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2586,10 +2592,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314787</v>
+        <v>131314778</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2629,10 +2635,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498341</v>
+        <v>498277</v>
       </c>
       <c r="R17" t="n">
-        <v>6980499</v>
+        <v>6980549</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2669,7 +2675,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2688,17 +2694,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2716,10 +2722,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314777</v>
+        <v>131314779</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2759,10 +2765,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498308</v>
+        <v>498295</v>
       </c>
       <c r="R18" t="n">
-        <v>6980576</v>
+        <v>6980533</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2799,7 +2805,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2818,17 +2824,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2846,10 +2852,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314782</v>
+        <v>131314780</v>
       </c>
       <c r="B19" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,10 +2895,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498337</v>
+        <v>498275</v>
       </c>
       <c r="R19" t="n">
-        <v>6980543</v>
+        <v>6980509</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2976,10 +2982,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314785</v>
+        <v>131314781</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3019,10 +3025,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498367</v>
+        <v>498293</v>
       </c>
       <c r="R20" t="n">
-        <v>6980539</v>
+        <v>6980509</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3059,7 +3065,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3078,17 +3084,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3106,10 +3112,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314780</v>
+        <v>131314782</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3149,10 +3155,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498275</v>
+        <v>498337</v>
       </c>
       <c r="R21" t="n">
-        <v>6980509</v>
+        <v>6980543</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3236,10 +3242,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314839</v>
+        <v>131314783</v>
       </c>
       <c r="B22" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3269,7 +3275,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3279,10 +3285,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498316</v>
+        <v>498390</v>
       </c>
       <c r="R22" t="n">
-        <v>6980493</v>
+        <v>6980556</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3319,7 +3325,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gammalt välsnidat bohål i en död/döende granstam på ca 2,5 meters höjd. Bohålets diameter ca 45 mm. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3366,10 +3372,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314786</v>
+        <v>131314784</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3409,10 +3415,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498353</v>
+        <v>498375</v>
       </c>
       <c r="R23" t="n">
-        <v>6980511</v>
+        <v>6980546</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3496,10 +3502,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314778</v>
+        <v>131314785</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3539,10 +3545,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498277</v>
+        <v>498367</v>
       </c>
       <c r="R24" t="n">
-        <v>6980549</v>
+        <v>6980539</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3626,10 +3632,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314789</v>
+        <v>131314786</v>
       </c>
       <c r="B25" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3659,7 +3665,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3669,10 +3675,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498066</v>
+        <v>498353</v>
       </c>
       <c r="R25" t="n">
-        <v>6980381</v>
+        <v>6980511</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,7 +3715,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3736,14 +3742,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3761,10 +3762,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131314773</v>
+        <v>131314787</v>
       </c>
       <c r="B26" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3804,10 +3805,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>498125</v>
+        <v>498341</v>
       </c>
       <c r="R26" t="n">
-        <v>6980508</v>
+        <v>6980499</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3844,7 +3845,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3863,17 +3864,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3894,7 +3895,7 @@
         <v>131314788</v>
       </c>
       <c r="B27" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4026,10 +4027,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314790</v>
+        <v>131314789</v>
       </c>
       <c r="B28" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4059,7 +4060,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4069,10 +4070,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498072</v>
+        <v>498066</v>
       </c>
       <c r="R28" t="n">
-        <v>6980389</v>
+        <v>6980381</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4109,7 +4110,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4136,9 +4137,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4156,10 +4162,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314779</v>
+        <v>131314790</v>
       </c>
       <c r="B29" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4199,10 +4205,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498295</v>
+        <v>498072</v>
       </c>
       <c r="R29" t="n">
-        <v>6980533</v>
+        <v>6980389</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4286,10 +4292,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131314783</v>
+        <v>131314791</v>
       </c>
       <c r="B30" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4319,7 +4325,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4329,10 +4335,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498390</v>
+        <v>498065</v>
       </c>
       <c r="R30" t="n">
-        <v>6980556</v>
+        <v>6980378</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4369,7 +4375,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4416,10 +4422,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131314775</v>
+        <v>131314792</v>
       </c>
       <c r="B31" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4449,7 +4455,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4459,10 +4465,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>498126</v>
+        <v>497998</v>
       </c>
       <c r="R31" t="n">
-        <v>6980530</v>
+        <v>6980370</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4499,7 +4505,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4546,10 +4552,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131314784</v>
+        <v>131314793</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4579,7 +4585,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4589,10 +4595,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>498375</v>
+        <v>497983</v>
       </c>
       <c r="R32" t="n">
-        <v>6980546</v>
+        <v>6980361</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4629,7 +4635,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4656,9 +4662,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4676,10 +4687,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131314774</v>
+        <v>131314794</v>
       </c>
       <c r="B33" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4719,10 +4730,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>498124</v>
+        <v>497922</v>
       </c>
       <c r="R33" t="n">
-        <v>6980534</v>
+        <v>6980314</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4786,9 +4797,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4806,10 +4822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131314806</v>
+        <v>131314839</v>
       </c>
       <c r="B34" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,26 +4833,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4844,10 +4865,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>498220</v>
+        <v>498316</v>
       </c>
       <c r="R34" t="n">
-        <v>6980720</v>
+        <v>6980493</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4882,13 +4903,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gammalt välsnidat bohål i en död/döende granstam på ca 2,5 meters höjd. Bohålets diameter ca 45 mm. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4927,27 +4952,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131314776</v>
+        <v>131314803</v>
       </c>
       <c r="B35" t="n">
-        <v>57904</v>
+        <v>57132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4955,25 +4980,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>498176</v>
+        <v>498066</v>
       </c>
       <c r="R35" t="n">
-        <v>6980749</v>
+        <v>6980662</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5008,11 +5041,6 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5025,21 +5053,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
